--- a/实用代码/陈子林.xlsx
+++ b/实用代码/陈子林.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A0D65264-EEE7-7B47-B2A4-DD5A552620DC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6CACA7CC-6D47-B847-BF07-E0892CA9A8BE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2500" yWindow="460" windowWidth="27440" windowHeight="15600" activeTab="1" xr2:uid="{DA82C8BD-A9B3-EB4F-860E-EF70CDDE766C}"/>
+    <workbookView xWindow="1080" yWindow="1460" windowWidth="27440" windowHeight="15560" activeTab="1" xr2:uid="{49F4269A-8020-4F43-BB42-394ACAB63C1D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="303">
   <si>
     <t>微信id</t>
   </si>
@@ -109,6 +109,12 @@
     <t>刘章郁</t>
   </si>
   <si>
+    <t>luofei1110</t>
+  </si>
+  <si>
+    <t>菲</t>
+  </si>
+  <si>
     <t>macyemily</t>
   </si>
   <si>
@@ -205,6 +211,12 @@
     <t>胡俊奕</t>
   </si>
   <si>
+    <t>wxid_0ki25dhdw07p21</t>
+  </si>
+  <si>
+    <t>Jeremy</t>
+  </si>
+  <si>
     <t>wxid_3x9s0fm3mhl221</t>
   </si>
   <si>
@@ -337,6 +349,12 @@
     <t>大欣</t>
   </si>
   <si>
+    <t>wxid_jxgxwvfvuu5321</t>
+  </si>
+  <si>
+    <t>静一静吖</t>
+  </si>
+  <si>
     <t>wxid_ke7ueomlwv7i22</t>
   </si>
   <si>
@@ -571,6 +589,12 @@
     <t>风若依</t>
   </si>
   <si>
+    <t>lisa718000</t>
+  </si>
+  <si>
+    <t>ฅIOKFATY</t>
+  </si>
+  <si>
     <t>mofalulu</t>
   </si>
   <si>
@@ -763,6 +787,12 @@
     <t>ㅤㅤㅤ</t>
   </si>
   <si>
+    <t>wxid_furivouhyebc11</t>
+  </si>
+  <si>
+    <t>璐璐Freya</t>
+  </si>
+  <si>
     <t>wxid_g0byzueznhq622</t>
   </si>
   <si>
@@ -793,6 +823,12 @@
     <t>Jocelyn</t>
   </si>
   <si>
+    <t>wxid_k4x0mpe3x66g22</t>
+  </si>
+  <si>
+    <t>烟雨江南</t>
+  </si>
+  <si>
     <t>wxid_kcnh1ibnq5c522</t>
   </si>
   <si>
@@ -827,6 +863,12 @@
   </si>
   <si>
     <t>天涯过客</t>
+  </si>
+  <si>
+    <t>wxid_q2ssiwp26cr521</t>
+  </si>
+  <si>
+    <t>兵未雪刃</t>
   </si>
   <si>
     <t>wxid_rszmr7ala6wc22</t>
@@ -1271,8 +1313,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87A2EF7D-4FB4-6F4E-B602-97567B0FB38F}">
-  <dimension ref="A1:I78"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBDD3594-7E4C-9D4E-BD45-698723AA1749}">
+  <dimension ref="A1:I81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1321,16 +1363,16 @@
         <v>2</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -1373,22 +1415,22 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1405,19 +1447,19 @@
         <v>4</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1431,22 +1473,22 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G6">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1460,22 +1502,22 @@
         <v>4</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -1518,22 +1560,22 @@
         <v>6</v>
       </c>
       <c r="D9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G9">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H9">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I9">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -1544,25 +1586,25 @@
         <v>26</v>
       </c>
       <c r="C10">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H10">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I10">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -1573,25 +1615,25 @@
         <v>28</v>
       </c>
       <c r="C11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D11">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E11">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1640,16 +1682,16 @@
         <v>4</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I13">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -1666,19 +1708,19 @@
         <v>4</v>
       </c>
       <c r="E14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I14">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1689,25 +1731,25 @@
         <v>36</v>
       </c>
       <c r="C15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H15">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I15">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1718,25 +1760,25 @@
         <v>38</v>
       </c>
       <c r="C16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I16">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1747,25 +1789,25 @@
         <v>40</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I17">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1776,25 +1818,25 @@
         <v>42</v>
       </c>
       <c r="C18">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D18">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E18">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F18">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G18">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1805,25 +1847,25 @@
         <v>44</v>
       </c>
       <c r="C19">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D19">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I19">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1834,25 +1876,25 @@
         <v>46</v>
       </c>
       <c r="C20">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D20">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E20">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F20">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G20">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H20">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I20">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1863,25 +1905,25 @@
         <v>48</v>
       </c>
       <c r="C21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I21">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1892,25 +1934,25 @@
         <v>50</v>
       </c>
       <c r="C22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D22">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E22">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F22">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G22">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H22">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I22">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1921,7 +1963,7 @@
         <v>52</v>
       </c>
       <c r="C23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D23">
         <v>4</v>
@@ -1930,16 +1972,16 @@
         <v>4</v>
       </c>
       <c r="F23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I23">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1950,25 +1992,25 @@
         <v>54</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1979,25 +2021,25 @@
         <v>56</v>
       </c>
       <c r="C25">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G25">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H25">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I25">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -2008,25 +2050,25 @@
         <v>58</v>
       </c>
       <c r="C26">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D26">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E26">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F26">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G26">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H26">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I26">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -2037,25 +2079,25 @@
         <v>60</v>
       </c>
       <c r="C27">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D27">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E27">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F27">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G27">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H27">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I27">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -2066,25 +2108,25 @@
         <v>62</v>
       </c>
       <c r="C28">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I28">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -2095,25 +2137,25 @@
         <v>64</v>
       </c>
       <c r="C29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I29">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -2124,25 +2166,25 @@
         <v>66</v>
       </c>
       <c r="C30">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E30">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F30">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G30">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H30">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I30">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -2182,7 +2224,7 @@
         <v>70</v>
       </c>
       <c r="C32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D32">
         <v>4</v>
@@ -2194,13 +2236,13 @@
         <v>4</v>
       </c>
       <c r="G32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I32">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -2211,25 +2253,25 @@
         <v>72</v>
       </c>
       <c r="C33">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D33">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E33">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F33">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G33">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H33">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I33">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -2240,25 +2282,25 @@
         <v>74</v>
       </c>
       <c r="C34">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D34">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E34">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F34">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G34">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H34">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I34">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -2269,25 +2311,25 @@
         <v>76</v>
       </c>
       <c r="C35">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D35">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E35">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F35">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G35">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H35">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I35">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -2298,25 +2340,25 @@
         <v>78</v>
       </c>
       <c r="C36">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D36">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E36">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F36">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G36">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H36">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I36">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -2330,22 +2372,22 @@
         <v>6</v>
       </c>
       <c r="D37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E37">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F37">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G37">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H37">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I37">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -2388,22 +2430,22 @@
         <v>6</v>
       </c>
       <c r="D39">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E39">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F39">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G39">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H39">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I39">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -2414,25 +2456,25 @@
         <v>86</v>
       </c>
       <c r="C40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E40">
         <v>6</v>
       </c>
       <c r="F40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I40">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -2446,22 +2488,22 @@
         <v>5</v>
       </c>
       <c r="D41">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E41">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F41">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G41">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H41">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I41">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -2475,22 +2517,22 @@
         <v>6</v>
       </c>
       <c r="D42">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E42">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F42">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G42">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H42">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I42">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -2501,25 +2543,25 @@
         <v>92</v>
       </c>
       <c r="C43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D43">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E43">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F43">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G43">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H43">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I43">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -2530,25 +2572,25 @@
         <v>94</v>
       </c>
       <c r="C44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I44">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -2559,25 +2601,25 @@
         <v>96</v>
       </c>
       <c r="C45">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D45">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E45">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F45">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G45">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H45">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I45">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -2588,25 +2630,25 @@
         <v>98</v>
       </c>
       <c r="C46">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D46">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E46">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F46">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G46">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H46">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I46">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -2617,25 +2659,25 @@
         <v>100</v>
       </c>
       <c r="C47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H47">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I47">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -2646,25 +2688,25 @@
         <v>102</v>
       </c>
       <c r="C48">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D48">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E48">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F48">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G48">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H48">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I48">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -2675,25 +2717,25 @@
         <v>104</v>
       </c>
       <c r="C49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D49">
         <v>4</v>
       </c>
       <c r="E49">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F49">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G49">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H49">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I49">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -2704,25 +2746,25 @@
         <v>106</v>
       </c>
       <c r="C50">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D50">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E50">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F50">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G50">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H50">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I50">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -2733,10 +2775,10 @@
         <v>108</v>
       </c>
       <c r="C51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E51">
         <v>3</v>
@@ -2762,25 +2804,25 @@
         <v>110</v>
       </c>
       <c r="C52">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D52">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E52">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F52">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G52">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H52">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I52">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -2794,22 +2836,22 @@
         <v>6</v>
       </c>
       <c r="D53">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E53">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F53">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G53">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H53">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I53">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -2829,16 +2871,16 @@
         <v>3</v>
       </c>
       <c r="F54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I54">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -2849,7 +2891,7 @@
         <v>116</v>
       </c>
       <c r="C55">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D55">
         <v>4</v>
@@ -2861,13 +2903,13 @@
         <v>4</v>
       </c>
       <c r="G55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H55">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I55">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -2878,25 +2920,25 @@
         <v>118</v>
       </c>
       <c r="C56">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D56">
         <v>5</v>
       </c>
       <c r="E56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F56">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G56">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H56">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I56">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -2907,25 +2949,25 @@
         <v>120</v>
       </c>
       <c r="C57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F57">
         <v>2</v>
       </c>
       <c r="G57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H57">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I57">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -2936,25 +2978,25 @@
         <v>122</v>
       </c>
       <c r="C58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D58">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E58">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F58">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G58">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H58">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I58">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -2965,25 +3007,25 @@
         <v>124</v>
       </c>
       <c r="C59">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D59">
         <v>4</v>
       </c>
       <c r="E59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H59">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I59">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -2994,25 +3036,25 @@
         <v>126</v>
       </c>
       <c r="C60">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D60">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E60">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F60">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G60">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H60">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I60">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -3023,19 +3065,19 @@
         <v>128</v>
       </c>
       <c r="C61">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D61">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H61">
         <v>2</v>
@@ -3058,19 +3100,19 @@
         <v>4</v>
       </c>
       <c r="E62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I62">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -3081,25 +3123,25 @@
         <v>132</v>
       </c>
       <c r="C63">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D63">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E63">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F63">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G63">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H63">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I63">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -3110,25 +3152,25 @@
         <v>134</v>
       </c>
       <c r="C64">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D64">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E64">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F64">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G64">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H64">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I64">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -3139,25 +3181,25 @@
         <v>136</v>
       </c>
       <c r="C65">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D65">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E65">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F65">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G65">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H65">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I65">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -3168,25 +3210,25 @@
         <v>138</v>
       </c>
       <c r="C66">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D66">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E66">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F66">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G66">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H66">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I66">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -3200,22 +3242,22 @@
         <v>5</v>
       </c>
       <c r="D67">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E67">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F67">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G67">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H67">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I67">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -3270,10 +3312,10 @@
         <v>6</v>
       </c>
       <c r="H69">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I69">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -3284,25 +3326,25 @@
         <v>146</v>
       </c>
       <c r="C70">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D70">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E70">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F70">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G70">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H70">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I70">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -3313,25 +3355,25 @@
         <v>148</v>
       </c>
       <c r="C71">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D71">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E71">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F71">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G71">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H71">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I71">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -3342,25 +3384,25 @@
         <v>150</v>
       </c>
       <c r="C72">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D72">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E72">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F72">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G72">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H72">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I72">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -3371,10 +3413,10 @@
         <v>152</v>
       </c>
       <c r="C73">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D73">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E73">
         <v>3</v>
@@ -3400,10 +3442,10 @@
         <v>154</v>
       </c>
       <c r="C74">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E74">
         <v>3</v>
@@ -3438,16 +3480,16 @@
         <v>6</v>
       </c>
       <c r="F75">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G75">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H75">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I75">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -3458,25 +3500,25 @@
         <v>158</v>
       </c>
       <c r="C76">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D76">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E76">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F76">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G76">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H76">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I76">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -3487,25 +3529,25 @@
         <v>160</v>
       </c>
       <c r="C77">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D77">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E77">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F77">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G77">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H77">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I77">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -3516,25 +3558,112 @@
         <v>162</v>
       </c>
       <c r="C78">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I78">
-        <v>2</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
+      <c r="A79" t="s">
+        <v>163</v>
+      </c>
+      <c r="B79" t="s">
+        <v>164</v>
+      </c>
+      <c r="C79">
+        <v>5</v>
+      </c>
+      <c r="D79">
+        <v>4</v>
+      </c>
+      <c r="E79">
+        <v>4</v>
+      </c>
+      <c r="F79">
+        <v>3</v>
+      </c>
+      <c r="G79">
+        <v>3</v>
+      </c>
+      <c r="H79">
+        <v>2</v>
+      </c>
+      <c r="I79">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
+      <c r="A80" t="s">
+        <v>165</v>
+      </c>
+      <c r="B80" t="s">
+        <v>166</v>
+      </c>
+      <c r="C80">
+        <v>5</v>
+      </c>
+      <c r="D80">
+        <v>3</v>
+      </c>
+      <c r="E80">
+        <v>3</v>
+      </c>
+      <c r="F80">
+        <v>3</v>
+      </c>
+      <c r="G80">
+        <v>3</v>
+      </c>
+      <c r="H80">
+        <v>3</v>
+      </c>
+      <c r="I80">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
+      <c r="A81" t="s">
+        <v>167</v>
+      </c>
+      <c r="B81" t="s">
+        <v>168</v>
+      </c>
+      <c r="C81">
+        <v>2</v>
+      </c>
+      <c r="D81">
+        <v>1</v>
+      </c>
+      <c r="E81">
+        <v>1</v>
+      </c>
+      <c r="F81">
+        <v>1</v>
+      </c>
+      <c r="G81">
+        <v>1</v>
+      </c>
+      <c r="H81">
+        <v>1</v>
+      </c>
+      <c r="I81">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3544,8 +3673,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE5FE9B4-4400-7949-921C-31050E837B4E}">
-  <dimension ref="A1:I65"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6F00F89-1922-9045-B0BD-12A4E3E1F686}">
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -3579,31 +3708,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C2" s="1">
         <v>4</v>
       </c>
       <c r="D2" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H2" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I2" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -3637,97 +3766,97 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="C4" s="1">
         <v>6</v>
       </c>
       <c r="D4" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E4" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F4" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G4" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H4" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I4" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="C5" s="1">
         <v>5</v>
       </c>
       <c r="D5" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E5" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F5" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H5" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I5" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="C6" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E6" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F6" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H6" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I6" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C7" s="1">
         <v>6</v>
@@ -3736,56 +3865,56 @@
         <v>6</v>
       </c>
       <c r="E7" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F7" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G7" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H7" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I7" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="C8" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D8" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E8" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F8" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H8" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I8" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C9" s="1">
         <v>3</v>
@@ -3794,291 +3923,291 @@
         <v>3</v>
       </c>
       <c r="E9" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F9" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H9" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I9" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C10" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D10" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E10" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F10" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H10" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I10" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C11" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D11" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E11" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F11" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H11" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I11" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C12" s="1">
         <v>5</v>
       </c>
       <c r="D12" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E12" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F12" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H12" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I12" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="C13" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D13" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E13" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F13" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G13" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H13" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I13" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C14" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D14" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E14" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F14" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G14" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H14" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I14" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C15" s="1">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D15" s="1">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E15" s="1">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F15" s="1">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G15" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H15" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I15" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="C16" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D16" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E16" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F16" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G16" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H16" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I16" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="1" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="C17" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D17" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E17" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F17" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G17" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H17" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I17" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="1" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="C18" s="1">
         <v>5</v>
       </c>
       <c r="D18" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E18" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F18" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G18" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H18" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I18" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="1" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="C19" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D19" s="1">
         <v>3</v>
@@ -4087,198 +4216,198 @@
         <v>3</v>
       </c>
       <c r="F19" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G19" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H19" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I19" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="1" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="C20" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D20" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E20" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F20" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H20" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I20" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="1" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="C21" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D21" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E21" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F21" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G21" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H21" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I21" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="1" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="C22" s="1">
         <v>5</v>
       </c>
       <c r="D22" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E22" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F22" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G22" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H22" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I22" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="1" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="C23" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D23" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E23" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F23" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G23" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H23" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I23" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="1" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="C24" s="1">
         <v>4</v>
       </c>
       <c r="D24" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E24" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F24" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G24" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H24" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I24" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="1" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C25" s="1">
         <v>4</v>
       </c>
       <c r="D25" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E25" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F25" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G25" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H25" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I25" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="1" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="C26" s="1">
         <v>4</v>
@@ -4287,85 +4416,85 @@
         <v>4</v>
       </c>
       <c r="E26" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F26" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G26" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H26" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I26" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="1" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="C27" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D27" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E27" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F27" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G27" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H27" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I27" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="1" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="C28" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D28" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E28" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F28" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G28" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H28" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I28" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="1" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C29" s="1">
         <v>4</v>
@@ -4377,56 +4506,56 @@
         <v>4</v>
       </c>
       <c r="F29" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G29" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H29" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I29" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="1" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="C30" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D30" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E30" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F30" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G30" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H30" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I30" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="1" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="C31" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D31" s="1">
         <v>4</v>
@@ -4449,161 +4578,161 @@
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="1" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C32" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D32" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E32" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F32" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G32" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H32" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I32" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="1" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="C33" s="1">
         <v>5</v>
       </c>
       <c r="D33" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E33" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F33" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G33" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H33" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I33" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="1" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="C34" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D34" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E34" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F34" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G34" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H34" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I34" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="1" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="C35" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D35" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E35" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F35" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G35" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H35" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I35" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="1" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="C36" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D36" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E36" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F36" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G36" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H36" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I36" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="1" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="C37" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D37" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37" s="1">
         <v>3</v>
@@ -4612,53 +4741,53 @@
         <v>3</v>
       </c>
       <c r="G37" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H37" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I37" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="1" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="C38" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D38" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E38" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F38" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G38" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H38" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I38" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="1" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="C39" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D39" s="1">
         <v>4</v>
@@ -4667,343 +4796,343 @@
         <v>4</v>
       </c>
       <c r="F39" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G39" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H39" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I39" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="1" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="C40" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D40" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E40" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F40" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G40" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H40" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I40" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="1" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="C41" s="1">
         <v>5</v>
       </c>
       <c r="D41" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E41" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F41" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G41" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H41" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I41" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="1" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="C42" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D42" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E42" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F42" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G42" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H42" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I42" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="1" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="C43" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D43" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E43" s="1">
         <v>3</v>
       </c>
       <c r="F43" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G43" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H43" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I43" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" s="1" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C44" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D44" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E44" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F44" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G44" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H44" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I44" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" s="1" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="C45" s="1">
         <v>3</v>
       </c>
       <c r="D45" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E45" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F45" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G45" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H45" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I45" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" s="1" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C46" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D46" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E46" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F46" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G46" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H46" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I46" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" s="1" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="C47" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D47" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E47" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F47" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G47" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H47" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I47" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" s="1" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="C48" s="1">
         <v>5</v>
       </c>
       <c r="D48" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E48" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F48" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G48" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H48" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I48" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" s="1" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="C49" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D49" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E49" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F49" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G49" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H49" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I49" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:9">
       <c r="A50" s="1" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C50" s="1">
         <v>5</v>
       </c>
       <c r="D50" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E50" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F50" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G50" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H50" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I50" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:9">
       <c r="A51" s="1" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="C51" s="1">
         <v>5</v>
@@ -5015,146 +5144,146 @@
         <v>5</v>
       </c>
       <c r="F51" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G51" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H51" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I51" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52" spans="1:9">
       <c r="A52" s="1" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="C52" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D52" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E52" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F52" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G52" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H52" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I52" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:9">
       <c r="A53" s="1" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C53" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D53" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E53" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F53" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G53" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H53" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I53" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:9">
       <c r="A54" s="1" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="C54" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D54" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E54" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F54" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G54" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H54" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I54" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55" spans="1:9">
       <c r="A55" s="1" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="C55" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D55" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E55" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F55" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G55" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H55" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I55" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:9">
       <c r="A56" s="1" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="C56" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D56" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E56" s="1">
         <v>3</v>
@@ -5163,166 +5292,166 @@
         <v>3</v>
       </c>
       <c r="G56" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H56" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I56" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:9">
       <c r="A57" s="1" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="C57" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D57" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E57" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F57" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G57" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H57" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I57" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:9">
       <c r="A58" s="1" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="C58" s="1">
         <v>5</v>
       </c>
       <c r="D58" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E58" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F58" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G58" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H58" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I58" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:9">
       <c r="A59" s="1" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="C59" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D59" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E59" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F59" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G59" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H59" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I59" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:9">
       <c r="A60" s="1" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C60" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D60" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E60" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F60" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G60" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H60" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I60" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:9">
       <c r="A61" s="1" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="C61" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D61" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E61" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F61" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G61" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H61" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I61" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:9">
       <c r="A62" s="1" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="C62" s="1">
         <v>5</v>
@@ -5331,106 +5460,222 @@
         <v>5</v>
       </c>
       <c r="E62" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F62" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G62" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H62" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I62" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:9">
       <c r="A63" s="1" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="C63" s="1">
         <v>5</v>
       </c>
       <c r="D63" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E63" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F63" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G63" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H63" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I63" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:9">
       <c r="A64" s="1" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="C64" s="1">
         <v>6</v>
       </c>
       <c r="D64" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E64" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F64" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G64" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H64" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I64" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65" spans="1:9">
       <c r="A65" s="1" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="C65" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D65" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E65" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F65" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G65" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H65" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I65" s="1">
-        <v>6</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
+      <c r="A66" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C66" s="1">
+        <v>4</v>
+      </c>
+      <c r="D66" s="1">
+        <v>4</v>
+      </c>
+      <c r="E66" s="1">
+        <v>3</v>
+      </c>
+      <c r="F66" s="1">
+        <v>2</v>
+      </c>
+      <c r="G66" s="1">
+        <v>1</v>
+      </c>
+      <c r="H66" s="1">
+        <v>0</v>
+      </c>
+      <c r="I66" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
+      <c r="A67" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C67" s="1">
+        <v>4</v>
+      </c>
+      <c r="D67" s="1">
+        <v>3</v>
+      </c>
+      <c r="E67" s="1">
+        <v>2</v>
+      </c>
+      <c r="F67" s="1">
+        <v>2</v>
+      </c>
+      <c r="G67" s="1">
+        <v>1</v>
+      </c>
+      <c r="H67" s="1">
+        <v>1</v>
+      </c>
+      <c r="I67" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
+      <c r="A68" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C68" s="1">
+        <v>5</v>
+      </c>
+      <c r="D68" s="1">
+        <v>5</v>
+      </c>
+      <c r="E68" s="1">
+        <v>5</v>
+      </c>
+      <c r="F68" s="1">
+        <v>4</v>
+      </c>
+      <c r="G68" s="1">
+        <v>4</v>
+      </c>
+      <c r="H68" s="1">
+        <v>4</v>
+      </c>
+      <c r="I68" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
+      <c r="A69" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C69" s="1">
+        <v>5</v>
+      </c>
+      <c r="D69" s="1">
+        <v>4</v>
+      </c>
+      <c r="E69" s="1">
+        <v>4</v>
+      </c>
+      <c r="F69" s="1">
+        <v>4</v>
+      </c>
+      <c r="G69" s="1">
+        <v>4</v>
+      </c>
+      <c r="H69" s="1">
+        <v>3</v>
+      </c>
+      <c r="I69" s="1">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
